--- a/2026/2DE MAYO/FEBRERO/2DEDMAYO-Febrero.xlsx
+++ b/2026/2DE MAYO/FEBRERO/2DEDMAYO-Febrero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\2DE MAYO\FEBRERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\2DE MAYO\FEBRERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070B734D-2963-44F9-93D3-5FAE3A9ED2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6039587C-E2FD-407B-8A88-E273655C38E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,20 +18,15 @@
     <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$M$37</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$107</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="136">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -409,6 +404,36 @@
   </si>
   <si>
     <t>MAIL:consorcio2demayo2813.15@gmail.com</t>
+  </si>
+  <si>
+    <t>Compra de bolsas Sra. Cecilia 5B</t>
+  </si>
+  <si>
+    <t>Mas Limpio - Compra de articulos de limpieza</t>
+  </si>
+  <si>
+    <t>Compra de Pendrive - Entrega administracion</t>
+  </si>
+  <si>
+    <t>Abona mediante</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Ingreso por pago de expensas</t>
+  </si>
+  <si>
+    <t>Ingreso pago x banco</t>
+  </si>
+  <si>
+    <t>Ingreso pago x efectivo</t>
+  </si>
+  <si>
+    <t>Transferencia realizada por administracion anterio a jacqueline Irma</t>
+  </si>
+  <si>
+    <t>Transf 28/01</t>
   </si>
 </sst>
 </file>
@@ -663,7 +688,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -1036,13 +1061,127 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1069,7 +1208,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -1119,9 +1257,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="10" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1259,13 +1394,43 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="11" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="18" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="18" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1311,6 +1476,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1319,66 +1544,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1394,18 +1559,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="18" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="16" fontId="18" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="13" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1484,9 +1649,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1524,9 +1689,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1559,26 +1724,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1611,26 +1759,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1804,60 +1935,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M111"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
-      <c r="B1" s="153" t="s">
+      <c r="B1" s="163" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="52"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="51"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="54"/>
-    </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="53"/>
+    </row>
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
-      <c r="B3" s="160" t="s">
+      <c r="B3" s="170" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="160"/>
-      <c r="D3" s="160"/>
-      <c r="E3" s="161"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="170"/>
+      <c r="D3" s="170"/>
+      <c r="E3" s="171"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="54" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>103</v>
       </c>
@@ -1865,12 +1996,12 @@
         <v>50</v>
       </c>
       <c r="C5" s="16"/>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="52" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
         <v>93</v>
       </c>
@@ -1881,57 +2012,57 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="163" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="173" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="163"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="163"/>
-      <c r="C9" s="163"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="163"/>
-      <c r="C10" s="163"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="162" t="s">
+      <c r="C8" s="173"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="173"/>
+      <c r="C9" s="173"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="173"/>
+      <c r="C10" s="173"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="172" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="162"/>
-      <c r="C13" s="162"/>
-      <c r="D13" s="162"/>
-      <c r="E13" s="162"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="162"/>
-      <c r="B14" s="162"/>
-      <c r="C14" s="162"/>
-      <c r="D14" s="162"/>
-      <c r="E14" s="162"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="162"/>
-      <c r="B15" s="162"/>
-      <c r="C15" s="162"/>
-      <c r="D15" s="162"/>
-      <c r="E15" s="162"/>
-    </row>
-    <row r="16" spans="1:5" ht="127.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="162"/>
-      <c r="B16" s="162"/>
-      <c r="C16" s="162"/>
-      <c r="D16" s="162"/>
-      <c r="E16" s="162"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="172"/>
+      <c r="C13" s="172"/>
+      <c r="D13" s="172"/>
+      <c r="E13" s="172"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="172"/>
+      <c r="B14" s="172"/>
+      <c r="C14" s="172"/>
+      <c r="D14" s="172"/>
+      <c r="E14" s="172"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="172"/>
+      <c r="B15" s="172"/>
+      <c r="C15" s="172"/>
+      <c r="D15" s="172"/>
+      <c r="E15" s="172"/>
+    </row>
+    <row r="16" spans="1:5" ht="127.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="172"/>
+      <c r="B16" s="172"/>
+      <c r="C16" s="172"/>
+      <c r="D16" s="172"/>
+      <c r="E16" s="172"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -1940,244 +2071,244 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-    </row>
-    <row r="22" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="156" t="s">
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+    </row>
+    <row r="22" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="166" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="157"/>
+      <c r="B22" s="167"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="109">
+      <c r="D22" s="107">
         <v>795882</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>94</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="109"/>
+      <c r="D23" s="107"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>95</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="109"/>
+      <c r="D24" s="107"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="109"/>
+      <c r="D25" s="107"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="45" t="s">
+    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="110">
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="108">
         <f>SUM(D22:D25)</f>
         <v>795882</v>
       </c>
-      <c r="E26" s="91"/>
+      <c r="E26" s="89"/>
       <c r="G26" s="21"/>
     </row>
-    <row r="27" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="109"/>
+      <c r="D27" s="107"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="23"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="109"/>
+      <c r="D28" s="107"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="109"/>
+      <c r="D29" s="107"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="111"/>
+      <c r="D30" s="109"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="111"/>
+      <c r="D31" s="109"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="45" t="s">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="112">
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="110">
         <f>SUM(D27:D31)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="91"/>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E32" s="89"/>
+    </row>
+    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B33" s="24"/>
       <c r="C33" s="24"/>
-      <c r="D33" s="113"/>
-      <c r="E33" s="92">
+      <c r="D33" s="111"/>
+      <c r="E33" s="90">
         <f>D26+D32</f>
         <v>795882</v>
       </c>
       <c r="F33" s="21"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="114"/>
-      <c r="E34" s="93"/>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="158" t="s">
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="112"/>
+      <c r="E34" s="91"/>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="168" t="s">
         <v>113</v>
       </c>
-      <c r="B35" s="159"/>
-      <c r="C35" s="42"/>
-      <c r="D35" s="109">
+      <c r="B35" s="169"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="107">
         <v>35000</v>
       </c>
-      <c r="E35" s="94" t="s">
+      <c r="E35" s="92" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="158" t="s">
+    <row r="36" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="168" t="s">
         <v>111</v>
       </c>
-      <c r="B36" s="159"/>
-      <c r="C36" s="42"/>
-      <c r="D36" s="115">
+      <c r="B36" s="169"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="113">
         <v>100000</v>
       </c>
-      <c r="E36" s="94" t="s">
+      <c r="E36" s="92" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="24" t="s">
         <v>15</v>
       </c>
       <c r="B37" s="24"/>
       <c r="C37" s="24"/>
-      <c r="D37" s="116"/>
-      <c r="E37" s="95">
+      <c r="D37" s="114"/>
+      <c r="E37" s="93">
         <f>SUM(D35:D36)</f>
         <v>135000</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="28" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="27" t="s">
         <v>26</v>
       </c>
       <c r="B38" s="24"/>
       <c r="C38" s="24"/>
-      <c r="D38" s="117"/>
-      <c r="E38" s="96"/>
-    </row>
-    <row r="39" spans="1:7" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="164" t="s">
+      <c r="D38" s="115"/>
+      <c r="E38" s="94"/>
+    </row>
+    <row r="39" spans="1:7" s="30" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="174" t="s">
         <v>101</v>
       </c>
-      <c r="B39" s="165"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="151">
+      <c r="B39" s="175"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="159">
         <v>60147</v>
       </c>
-      <c r="E39" s="197" t="s">
+      <c r="E39" s="161" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="166"/>
-      <c r="B40" s="167"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="152"/>
-      <c r="E40" s="198"/>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="176"/>
+      <c r="B40" s="177"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="160"/>
+      <c r="E40" s="162"/>
+    </row>
+    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="24" t="s">
         <v>2</v>
       </c>
       <c r="B41" s="24"/>
       <c r="C41" s="24"/>
-      <c r="D41" s="116"/>
-      <c r="E41" s="97">
+      <c r="D41" s="114"/>
+      <c r="E41" s="95">
         <f>SUM(D39:D40)</f>
         <v>60147</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="28" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B42" s="98"/>
-      <c r="C42" s="98"/>
-      <c r="D42" s="118"/>
-      <c r="E42" s="99"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="96"/>
+      <c r="C42" s="96"/>
+      <c r="D42" s="116"/>
+      <c r="E42" s="97"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B43" s="5"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="29">
+      <c r="C43" s="41"/>
+      <c r="D43" s="28">
         <v>510495.04</v>
       </c>
-      <c r="E43" s="104" t="s">
+      <c r="E43" s="102" t="s">
         <v>110</v>
       </c>
-      <c r="G43" s="79"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G43" s="77"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>51</v>
       </c>
@@ -2185,14 +2316,14 @@
         <v>117</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="119">
+      <c r="D44" s="117">
         <v>46493.49</v>
       </c>
-      <c r="E44" s="104" t="s">
+      <c r="E44" s="102" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="str">
         <f>A44</f>
         <v>Sindicatos mes de FEBRERO</v>
@@ -2201,15 +2332,15 @@
         <v>116</v>
       </c>
       <c r="C45" s="5"/>
-      <c r="D45" s="119">
+      <c r="D45" s="117">
         <v>107821.05</v>
       </c>
-      <c r="E45" s="105" t="str">
+      <c r="E45" s="103" t="str">
         <f>E44</f>
         <v>Debito 12/02</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="str">
         <f>A45</f>
         <v>Sindicatos mes de FEBRERO</v>
@@ -2218,499 +2349,573 @@
         <v>115</v>
       </c>
       <c r="C46" s="5"/>
-      <c r="D46" s="119">
+      <c r="D46" s="117">
         <v>5165.9399999999996</v>
       </c>
-      <c r="E46" s="106" t="str">
+      <c r="E46" s="104" t="str">
         <f>E45</f>
         <v>Debito 12/02</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="98"/>
-      <c r="C47" s="98"/>
-      <c r="D47" s="120"/>
-      <c r="E47" s="97">
+      <c r="B47" s="96"/>
+      <c r="C47" s="96"/>
+      <c r="D47" s="118"/>
+      <c r="E47" s="95">
         <f>SUM(D43:D46)</f>
         <v>669975.52</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="28" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B48" s="98"/>
-      <c r="C48" s="98"/>
-      <c r="D48" s="118"/>
-      <c r="E48" s="99"/>
-    </row>
-    <row r="49" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="96"/>
+      <c r="C48" s="96"/>
+      <c r="D48" s="116"/>
+      <c r="E48" s="97"/>
+    </row>
+    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>97</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="119">
+      <c r="D49" s="117">
         <v>379309.22</v>
       </c>
-      <c r="E49" s="104" t="s">
+      <c r="E49" s="102" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="148" t="s">
+    <row r="50" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="146" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="149"/>
+      <c r="B50" s="147"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="119">
+      <c r="D50" s="117">
         <v>307229.90000000002</v>
       </c>
-      <c r="E50" s="104" t="s">
+      <c r="E50" s="102" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="24" t="s">
         <v>4</v>
       </c>
       <c r="B51" s="24"/>
       <c r="C51" s="24"/>
-      <c r="D51" s="121"/>
-      <c r="E51" s="97">
+      <c r="D51" s="119"/>
+      <c r="E51" s="95">
         <f>SUM(D49:D50)</f>
         <v>686539.12</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="28"/>
+    <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="27"/>
       <c r="B52" s="24"/>
       <c r="C52" s="24"/>
-      <c r="D52" s="116"/>
-      <c r="E52" s="100"/>
-    </row>
-    <row r="53" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="107" t="s">
+      <c r="D52" s="114"/>
+      <c r="E52" s="98"/>
+    </row>
+    <row r="53" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="105" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="103"/>
+      <c r="B53" s="101"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="119">
+      <c r="D53" s="117">
         <v>22794.799999999999</v>
       </c>
-      <c r="E53" s="104" t="s">
+      <c r="E53" s="102" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="107" t="s">
+    <row r="54" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="B54" s="103"/>
+      <c r="B54" s="101"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="119">
+      <c r="D54" s="117">
         <v>125300</v>
       </c>
-      <c r="E54" s="150" t="s">
+      <c r="E54" s="158" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="24" t="s">
+    <row r="55" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="105" t="s">
+        <v>134</v>
+      </c>
+      <c r="B55" s="101"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="117">
+        <v>400000</v>
+      </c>
+      <c r="E55" s="157" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="105" t="s">
+        <v>134</v>
+      </c>
+      <c r="B56" s="101"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="117">
+        <v>280000</v>
+      </c>
+      <c r="E56" s="157" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="101">
-        <f>SUM(D53:D54)</f>
-        <v>148094.79999999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="28" t="s">
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="99">
+        <f>SUM(D53:D56)</f>
+        <v>828094.8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="B56" s="50"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="113"/>
-      <c r="E56" s="100"/>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
+      <c r="B58" s="49"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="98"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="119">
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="117">
         <v>57500</v>
       </c>
-      <c r="E57" s="102"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
+      <c r="E59" s="100"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="119">
-        <v>52473.43</v>
-      </c>
-      <c r="E58" s="32"/>
-    </row>
-    <row r="59" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" s="41"/>
-      <c r="C59" s="41"/>
-      <c r="D59" s="65"/>
-      <c r="E59" s="60">
-        <f>SUM(D57:D58)</f>
-        <v>109973.43</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="59"/>
-      <c r="E60" s="66"/>
-    </row>
-    <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="25" t="s">
+      <c r="D60" s="117">
+        <f>1141+52473.43</f>
+        <v>53614.43</v>
+      </c>
+      <c r="E60" s="31"/>
+    </row>
+    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" s="40"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="58">
+        <f>SUM(D59:D60)</f>
+        <v>111114.43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="57"/>
+      <c r="E62" s="64"/>
+    </row>
+    <row r="63" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="68">
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="65"/>
+      <c r="E63" s="66">
         <f>3800000-2605611.87</f>
         <v>1194388.1299999999</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="1"/>
-      <c r="D62" s="69"/>
-      <c r="E62" s="70"/>
-      <c r="F62" s="34"/>
-    </row>
-    <row r="63" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
+    <row r="64" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="1"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="68"/>
+      <c r="F64" s="33"/>
+    </row>
+    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B63" s="9"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="71"/>
-      <c r="E63" s="72">
-        <f>(SUM(E29:E61))</f>
-        <v>3800000</v>
-      </c>
-      <c r="F63" s="90"/>
-      <c r="G63" s="34"/>
-      <c r="H63" s="79"/>
-      <c r="I63" s="79"/>
-      <c r="J63" s="79"/>
-      <c r="K63" s="79"/>
-      <c r="L63" s="79"/>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D64" s="69"/>
-      <c r="E64" s="69"/>
-      <c r="H64" s="79"/>
-      <c r="I64" s="79"/>
-      <c r="J64" s="79"/>
-      <c r="K64" s="79"/>
-      <c r="L64" s="79"/>
-    </row>
-    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="9"/>
+      <c r="C65" s="4"/>
       <c r="D65" s="69"/>
-      <c r="E65" s="69"/>
-      <c r="H65" s="108"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="10" t="s">
+      <c r="E65" s="70">
+        <f>(SUM(E29:E63))</f>
+        <v>4481141</v>
+      </c>
+      <c r="F65" s="88"/>
+      <c r="G65" s="33"/>
+      <c r="H65" s="77"/>
+      <c r="I65" s="77"/>
+      <c r="J65" s="77"/>
+      <c r="K65" s="77"/>
+      <c r="L65" s="77"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D66" s="67"/>
+      <c r="E66" s="67"/>
+      <c r="H66" s="77"/>
+      <c r="I66" s="77"/>
+      <c r="J66" s="77"/>
+      <c r="K66" s="77"/>
+      <c r="L66" s="77"/>
+    </row>
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D67" s="67"/>
+      <c r="E67" s="67"/>
+      <c r="H67" s="106"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B66" s="11"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="73"/>
-      <c r="E66" s="74"/>
-    </row>
-    <row r="67" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="156"/>
-      <c r="B67" s="157"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="82"/>
-      <c r="E67" s="61"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="156"/>
-      <c r="B68" s="157"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="63"/>
-      <c r="E68" s="61"/>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="158"/>
-      <c r="B69" s="159"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="72"/>
+    </row>
+    <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="166"/>
+      <c r="B69" s="167"/>
       <c r="C69" s="5"/>
-      <c r="D69" s="63"/>
-      <c r="E69" s="61"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="62"/>
-      <c r="B70" s="64"/>
+      <c r="D69" s="80"/>
+      <c r="E69" s="59"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="166"/>
+      <c r="B70" s="167"/>
       <c r="C70" s="5"/>
-      <c r="D70" s="63"/>
-      <c r="E70" s="61"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="39"/>
-      <c r="B71" s="38"/>
-      <c r="C71" s="38"/>
-      <c r="D71" s="46"/>
-      <c r="E71" s="46">
-        <f>SUM(D67:D70)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="25" t="s">
+      <c r="D70" s="61"/>
+      <c r="E70" s="59"/>
+    </row>
+    <row r="71" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="168"/>
+      <c r="B71" s="169"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="61"/>
+      <c r="E71" s="59"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="60"/>
+      <c r="B72" s="62"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="61"/>
+      <c r="E72" s="59"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="38"/>
+      <c r="B73" s="37"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="45"/>
+      <c r="E73" s="45">
+        <f>SUM(D69:D72)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="210" t="s">
         <v>19</v>
       </c>
-      <c r="B74" s="25"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="26"/>
-      <c r="E74" s="58"/>
-    </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="3" t="s">
+      <c r="B76" s="211"/>
+      <c r="C76" s="211"/>
+      <c r="D76" s="212"/>
+      <c r="E76" s="209"/>
+    </row>
+    <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B76" s="9"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="51">
-        <f>E71+E74</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="56" t="s">
+      <c r="B78" s="9"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="50">
+        <f>E73+E76</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B78" s="57">
-        <f>E63</f>
-        <v>3800000</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="56" t="s">
+      <c r="B80" s="56">
+        <f>E65</f>
+        <v>4481141</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B79" s="57">
-        <f>E63-E61</f>
-        <v>2605611.87</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="56" t="s">
+      <c r="B81" s="56">
+        <f>E65-E63</f>
+        <v>3286752.87</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B80" s="57">
-        <f>E76-E74</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="56" t="s">
+      <c r="B82" s="56">
+        <f>E78-E76</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="B81" s="57">
-        <f>E76</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="83" t="s">
+      <c r="B83" s="56">
+        <f>E78</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="B84" s="84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="43" t="s">
+      <c r="B86" s="82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="148" t="s">
+        <v>131</v>
+      </c>
+      <c r="B87" s="149">
+        <f>PRORRATEO!G38</f>
+        <v>519037.4</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="33"/>
+      <c r="E87" s="78"/>
+      <c r="F87" s="79"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="148" t="s">
+        <v>126</v>
+      </c>
+      <c r="B88" s="149">
+        <v>-7000</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="33"/>
+      <c r="E88" s="78"/>
+      <c r="F88" s="79"/>
+    </row>
+    <row r="89" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A89" s="150" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89" s="149">
+        <v>-15600</v>
+      </c>
+      <c r="C89" s="22"/>
+      <c r="D89" s="33"/>
+      <c r="E89" s="78"/>
+      <c r="F89" s="79"/>
+    </row>
+    <row r="90" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A90" s="150" t="s">
+        <v>127</v>
+      </c>
+      <c r="B90" s="149">
+        <v>-11000</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="33"/>
+      <c r="E90" s="78"/>
+      <c r="F90" s="79"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="153"/>
+      <c r="B91" s="154"/>
+      <c r="C91" s="22"/>
+      <c r="D91" s="33"/>
+      <c r="E91" s="78"/>
+      <c r="F91" s="79"/>
+    </row>
+    <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="151" t="s">
+        <v>39</v>
+      </c>
+      <c r="B92" s="152">
+        <f>SUM(B86:C91)</f>
+        <v>485437.4</v>
+      </c>
+      <c r="C92" s="22"/>
+    </row>
+    <row r="93" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A93"/>
+      <c r="B93" s="32"/>
+      <c r="C93" s="29"/>
+    </row>
+    <row r="94" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="B94" s="82">
+        <v>321565.45</v>
+      </c>
+      <c r="C94" s="29"/>
+      <c r="D94" s="36"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B95" s="86">
+        <f>-B81</f>
+        <v>-3286752.87</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B96" s="86">
+        <f>-B82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A97" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B97" s="86">
+        <f>B106</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="B85" s="89">
-        <v>502650</v>
-      </c>
-      <c r="C85" s="22"/>
-      <c r="D85" s="34"/>
-      <c r="E85" s="80"/>
-      <c r="F85" s="81"/>
-    </row>
-    <row r="86" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="86" t="s">
+      <c r="B98" s="87">
+        <f>PRORRATEO!G37</f>
+        <v>3642735.4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="B86" s="87">
-        <f>SUM(B84:C85)</f>
-        <v>502650</v>
-      </c>
-      <c r="C86" s="22"/>
-    </row>
-    <row r="87" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87"/>
-      <c r="B87" s="33"/>
-      <c r="C87" s="30"/>
-    </row>
-    <row r="88" spans="1:6" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="83" t="s">
-        <v>46</v>
-      </c>
-      <c r="B88" s="84">
-        <v>321565.45</v>
-      </c>
-      <c r="C88" s="30"/>
-      <c r="D88" s="37"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="B89" s="88">
-        <f>-B79</f>
-        <v>-2605611.87</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B90" s="88">
-        <f>-B80</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="B91" s="88">
-        <f>B100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="B92" s="89">
-        <f>PRORRATEO!G36</f>
-        <v>2961293.3999999994</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="86" t="s">
-        <v>39</v>
-      </c>
-      <c r="B93" s="87">
-        <f>SUM(B88:C92)</f>
-        <v>677246.97999999952</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="85"/>
-      <c r="B94" s="85"/>
-    </row>
-    <row r="95" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="155" t="s">
+      <c r="B99" s="85">
+        <f>SUM(B94:C98)</f>
+        <v>677547.98</v>
+      </c>
+      <c r="D99" s="32"/>
+      <c r="E99" s="33"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A100" s="83"/>
+      <c r="B100" s="83"/>
+    </row>
+    <row r="101" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A102" s="165" t="s">
         <v>27</v>
       </c>
-      <c r="B96" s="155"/>
-      <c r="C96" s="155"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A97" s="155"/>
-      <c r="B97" s="155"/>
-      <c r="C97" s="155"/>
-    </row>
-    <row r="98" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="76"/>
-      <c r="B98" s="29"/>
-      <c r="C98" s="29">
+      <c r="B102" s="165"/>
+      <c r="C102" s="165"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A103" s="165"/>
+      <c r="B103" s="165"/>
+      <c r="C103" s="165"/>
+    </row>
+    <row r="104" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="74"/>
+      <c r="B104" s="28"/>
+      <c r="C104" s="28">
         <v>40000</v>
       </c>
-      <c r="E98" s="90"/>
-    </row>
-    <row r="99" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="76"/>
-      <c r="B99" s="78"/>
-      <c r="C99" s="75"/>
-      <c r="D99" s="90"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="35" t="s">
+      <c r="E104" s="88"/>
+    </row>
+    <row r="105" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="74"/>
+      <c r="B105" s="76"/>
+      <c r="C105" s="73"/>
+      <c r="D105" s="88"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A106" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B100" s="77">
-        <f>SUM(B98:B99)</f>
-        <v>0</v>
-      </c>
-      <c r="C100" s="36"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M101" s="7"/>
-    </row>
-    <row r="102" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="154"/>
-      <c r="B102" s="154"/>
-      <c r="C102" s="154"/>
-      <c r="D102" s="154"/>
-      <c r="E102" s="154"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A103" s="154"/>
-      <c r="B103" s="154"/>
-      <c r="C103" s="154"/>
-      <c r="D103" s="154"/>
-      <c r="E103" s="154"/>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A104" s="154"/>
-      <c r="B104" s="154"/>
-      <c r="C104" s="154"/>
-      <c r="D104" s="154"/>
-      <c r="E104" s="154"/>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A105" s="154"/>
-      <c r="B105" s="154"/>
-      <c r="C105" s="154"/>
-      <c r="D105" s="154"/>
-      <c r="E105" s="154"/>
+      <c r="B106" s="75">
+        <f>SUM(B104:B105)</f>
+        <v>0</v>
+      </c>
+      <c r="C106" s="35"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M107" s="7"/>
+    </row>
+    <row r="108" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="164"/>
+      <c r="B108" s="164"/>
+      <c r="C108" s="164"/>
+      <c r="D108" s="164"/>
+      <c r="E108" s="164"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A109" s="164"/>
+      <c r="B109" s="164"/>
+      <c r="C109" s="164"/>
+      <c r="D109" s="164"/>
+      <c r="E109" s="164"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A110" s="164"/>
+      <c r="B110" s="164"/>
+      <c r="C110" s="164"/>
+      <c r="D110" s="164"/>
+      <c r="E110" s="164"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A111" s="164"/>
+      <c r="B111" s="164"/>
+      <c r="C111" s="164"/>
+      <c r="D111" s="164"/>
+      <c r="E111" s="164"/>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="D39:D40"/>
     <mergeCell ref="E39:E40"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="A102:E105"/>
-    <mergeCell ref="A96:C97"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A108:E111"/>
+    <mergeCell ref="A102:C103"/>
+    <mergeCell ref="A70:B70"/>
     <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A71:B71"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="B3:E3"/>
@@ -2727,70 +2932,72 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q54"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="0.109375" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" customWidth="1"/>
+    <col min="11" max="12" width="12.44140625" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
-      <c r="K1" s="172"/>
-      <c r="L1" s="172"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+      <c r="L1" s="178"/>
+      <c r="M1" s="178"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="200">
-        <v>0</v>
-      </c>
-      <c r="E2" s="200"/>
+      <c r="D2" s="208">
+        <v>0</v>
+      </c>
+      <c r="E2" s="208"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6" t="s">
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="K2" s="199">
-        <f>O2</f>
+      <c r="L2" s="207">
+        <f>P2</f>
         <v>3800000</v>
       </c>
-      <c r="L2" s="199"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="21"/>
-      <c r="O2">
+      <c r="M2" s="207"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="21"/>
+      <c r="P2">
         <v>3800000</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2802,1489 +3009,1610 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-    </row>
-    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="181" t="str">
+      <c r="L3" s="6"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+    </row>
+    <row r="4" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="187" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="B4" s="182"/>
-      <c r="C4" s="182"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="182"/>
-      <c r="F4" s="182"/>
-      <c r="G4" s="182"/>
-      <c r="H4" s="182"/>
-      <c r="I4" s="182"/>
-      <c r="J4" s="182"/>
-      <c r="K4" s="182"/>
-      <c r="L4" s="182"/>
-      <c r="M4" s="183"/>
-    </row>
-    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="184"/>
-      <c r="B5" s="185"/>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="185"/>
-      <c r="I5" s="185"/>
-      <c r="J5" s="185"/>
-      <c r="K5" s="185"/>
-      <c r="L5" s="185"/>
-      <c r="M5" s="186"/>
-    </row>
-    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="184"/>
-      <c r="B6" s="185"/>
-      <c r="C6" s="185"/>
-      <c r="D6" s="185"/>
-      <c r="E6" s="185"/>
-      <c r="F6" s="185"/>
-      <c r="G6" s="185"/>
-      <c r="H6" s="185"/>
-      <c r="I6" s="185"/>
-      <c r="J6" s="185"/>
-      <c r="K6" s="185"/>
-      <c r="L6" s="185"/>
-      <c r="M6" s="186"/>
-    </row>
-    <row r="7" spans="1:16" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="184"/>
-      <c r="B7" s="185"/>
-      <c r="C7" s="185"/>
-      <c r="D7" s="185"/>
-      <c r="E7" s="185"/>
-      <c r="F7" s="185"/>
-      <c r="G7" s="185"/>
-      <c r="H7" s="185"/>
-      <c r="I7" s="185"/>
-      <c r="J7" s="185"/>
-      <c r="K7" s="185"/>
-      <c r="L7" s="185"/>
-      <c r="M7" s="186"/>
-    </row>
-    <row r="8" spans="1:16" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="187"/>
-      <c r="B8" s="188"/>
-      <c r="C8" s="188"/>
-      <c r="D8" s="188"/>
-      <c r="E8" s="188"/>
-      <c r="F8" s="188"/>
-      <c r="G8" s="188"/>
-      <c r="H8" s="188"/>
-      <c r="I8" s="188"/>
-      <c r="J8" s="188"/>
-      <c r="K8" s="188"/>
-      <c r="L8" s="188"/>
-      <c r="M8" s="189"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="173" t="s">
+      <c r="B4" s="188"/>
+      <c r="C4" s="188"/>
+      <c r="D4" s="188"/>
+      <c r="E4" s="188"/>
+      <c r="F4" s="188"/>
+      <c r="G4" s="188"/>
+      <c r="H4" s="188"/>
+      <c r="I4" s="188"/>
+      <c r="J4" s="188"/>
+      <c r="K4" s="188"/>
+      <c r="L4" s="188"/>
+      <c r="M4" s="188"/>
+      <c r="N4" s="189"/>
+    </row>
+    <row r="5" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="190"/>
+      <c r="B5" s="191"/>
+      <c r="C5" s="191"/>
+      <c r="D5" s="191"/>
+      <c r="E5" s="191"/>
+      <c r="F5" s="191"/>
+      <c r="G5" s="191"/>
+      <c r="H5" s="191"/>
+      <c r="I5" s="191"/>
+      <c r="J5" s="191"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="191"/>
+      <c r="N5" s="192"/>
+    </row>
+    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="190"/>
+      <c r="B6" s="191"/>
+      <c r="C6" s="191"/>
+      <c r="D6" s="191"/>
+      <c r="E6" s="191"/>
+      <c r="F6" s="191"/>
+      <c r="G6" s="191"/>
+      <c r="H6" s="191"/>
+      <c r="I6" s="191"/>
+      <c r="J6" s="191"/>
+      <c r="K6" s="191"/>
+      <c r="L6" s="191"/>
+      <c r="M6" s="191"/>
+      <c r="N6" s="192"/>
+    </row>
+    <row r="7" spans="1:17" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="190"/>
+      <c r="B7" s="191"/>
+      <c r="C7" s="191"/>
+      <c r="D7" s="191"/>
+      <c r="E7" s="191"/>
+      <c r="F7" s="191"/>
+      <c r="G7" s="191"/>
+      <c r="H7" s="191"/>
+      <c r="I7" s="191"/>
+      <c r="J7" s="191"/>
+      <c r="K7" s="191"/>
+      <c r="L7" s="191"/>
+      <c r="M7" s="191"/>
+      <c r="N7" s="192"/>
+    </row>
+    <row r="8" spans="1:17" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="193"/>
+      <c r="B8" s="194"/>
+      <c r="C8" s="194"/>
+      <c r="D8" s="194"/>
+      <c r="E8" s="194"/>
+      <c r="F8" s="194"/>
+      <c r="G8" s="194"/>
+      <c r="H8" s="194"/>
+      <c r="I8" s="194"/>
+      <c r="J8" s="194"/>
+      <c r="K8" s="194"/>
+      <c r="L8" s="194"/>
+      <c r="M8" s="194"/>
+      <c r="N8" s="195"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="179" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="175" t="s">
+      <c r="B9" s="181" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="175" t="s">
+      <c r="C9" s="181" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="145"/>
-      <c r="E9" s="175" t="s">
+      <c r="D9" s="143"/>
+      <c r="E9" s="181" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="173" t="s">
+      <c r="F9" s="179" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="175" t="s">
+      <c r="G9" s="181" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="177" t="s">
+      <c r="H9" s="181" t="s">
+        <v>129</v>
+      </c>
+      <c r="I9" s="183" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="173" t="s">
+      <c r="J9" s="179" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="173" t="s">
+      <c r="K9" s="179" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="179" t="s">
+      <c r="L9" s="185" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="49" t="s">
+      <c r="M9" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="168" t="s">
+      <c r="N9" s="198" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="190"/>
-      <c r="B10" s="191"/>
-      <c r="C10" s="176"/>
-      <c r="D10" s="146"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="174"/>
-      <c r="G10" s="176"/>
-      <c r="H10" s="178"/>
-      <c r="I10" s="174"/>
-      <c r="J10" s="174"/>
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="196"/>
+      <c r="B10" s="197"/>
+      <c r="C10" s="182"/>
+      <c r="D10" s="144"/>
+      <c r="E10" s="182"/>
+      <c r="F10" s="180"/>
+      <c r="G10" s="182"/>
+      <c r="H10" s="197"/>
+      <c r="I10" s="184"/>
+      <c r="J10" s="180"/>
       <c r="K10" s="180"/>
-      <c r="L10" s="48" t="str">
+      <c r="L10" s="186"/>
+      <c r="M10" s="47" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/03</v>
       </c>
-      <c r="M10" s="169"/>
-    </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="122" t="s">
+      <c r="N10" s="199"/>
+    </row>
+    <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="120" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="122" t="s">
+      <c r="B11" s="120" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="122" t="s">
+      <c r="C11" s="120" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="122"/>
-      <c r="E11" s="143">
+      <c r="D11" s="120"/>
+      <c r="E11" s="141">
         <v>6.18</v>
       </c>
-      <c r="F11" s="124">
+      <c r="F11" s="122">
         <v>283765</v>
       </c>
-      <c r="G11" s="125"/>
-      <c r="H11" s="126">
-        <f t="shared" ref="H11:H35" si="0">F11-G11</f>
+      <c r="G11" s="123">
+        <f>F11</f>
         <v>283765</v>
       </c>
-      <c r="I11" s="126">
-        <f>IF(H11&gt;0,H11*3%,0)</f>
-        <v>8512.9499999999989</v>
-      </c>
-      <c r="J11" s="127">
-        <f>K$2*E11/100</f>
+      <c r="H11" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="124">
+        <f t="shared" ref="I11:I35" si="0">F11-G11</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="124">
+        <f>IF(I11&gt;0,I11*3%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="125">
+        <f>L$2*E11/100</f>
         <v>234840</v>
       </c>
-      <c r="K11" s="128">
+      <c r="L11" s="126">
         <f>D$2*E11/100</f>
         <v>0</v>
       </c>
-      <c r="L11" s="129">
-        <f t="shared" ref="L11:L35" si="1">ROUND(SUM(H11:K11),0) + N11</f>
-        <v>527118.01</v>
-      </c>
-      <c r="M11" s="130">
-        <f t="shared" ref="M11:M35" si="2">ROUND(L11*3%,0) + L11</f>
-        <v>542932.01</v>
-      </c>
-      <c r="N11" s="34">
+      <c r="M11" s="127">
+        <f t="shared" ref="M11:M35" si="1">ROUND(SUM(I11:L11),0) + O11</f>
+        <v>234840.01</v>
+      </c>
+      <c r="N11" s="128">
+        <f t="shared" ref="N11:N35" si="2">ROUND(M11*3%,0) + M11</f>
+        <v>241885.01</v>
+      </c>
+      <c r="O11" s="33">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="122" t="s">
+      <c r="P11" s="33"/>
+    </row>
+    <row r="12" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="120" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="122" t="s">
+      <c r="B12" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="122" t="s">
+      <c r="C12" s="120" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="122" t="s">
+      <c r="D12" s="120" t="s">
         <v>120</v>
       </c>
-      <c r="E12" s="143">
+      <c r="E12" s="141">
         <v>4.33</v>
       </c>
-      <c r="F12" s="124">
+      <c r="F12" s="122">
         <v>198819</v>
       </c>
-      <c r="G12" s="125">
+      <c r="G12" s="123">
         <f>F12</f>
         <v>198819</v>
       </c>
-      <c r="H12" s="126">
+      <c r="H12" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="126">
-        <f t="shared" ref="I12:I35" si="3">IF(H12&gt;0,H12*3%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="127">
-        <f t="shared" ref="J12:J35" si="4">K$2*E12/100</f>
+      <c r="J12" s="124">
+        <f t="shared" ref="J12:J35" si="3">IF(I12&gt;0,I12*3%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="125">
+        <f t="shared" ref="K12:K35" si="4">L$2*E12/100</f>
         <v>164540</v>
       </c>
-      <c r="K12" s="128">
-        <f t="shared" ref="K12:K35" si="5">D$2*E12/100</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="129">
+      <c r="L12" s="126">
+        <f t="shared" ref="L12:L35" si="5">D$2*E12/100</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="127">
         <f t="shared" si="1"/>
         <v>164540.01999999999</v>
       </c>
-      <c r="M12" s="130">
+      <c r="N12" s="128">
         <f t="shared" si="2"/>
         <v>169476.02</v>
       </c>
-      <c r="N12" s="34">
-        <f>N11+0.01</f>
+      <c r="O12" s="33">
+        <f>O11+0.01</f>
         <v>0.02</v>
       </c>
-      <c r="O12" s="34"/>
-    </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="131" t="s">
+      <c r="P12" s="33"/>
+    </row>
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="131" t="s">
+      <c r="B13" s="129" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="131" t="s">
+      <c r="C13" s="129" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="131"/>
-      <c r="E13" s="144">
+      <c r="D13" s="129"/>
+      <c r="E13" s="142">
         <v>6.18</v>
       </c>
-      <c r="F13" s="132">
+      <c r="F13" s="130">
         <v>277857</v>
       </c>
-      <c r="G13" s="125">
+      <c r="G13" s="123">
         <f>320000-G30</f>
         <v>284515.59999999998</v>
       </c>
-      <c r="H13" s="126">
+      <c r="H13" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="124">
         <f t="shared" si="0"/>
         <v>-6658.5999999999767</v>
       </c>
-      <c r="I13" s="126">
+      <c r="J13" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J13" s="127">
+      <c r="K13" s="125">
         <f t="shared" si="4"/>
         <v>234840</v>
       </c>
-      <c r="K13" s="128">
+      <c r="L13" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L13" s="129">
+      <c r="M13" s="127">
         <f t="shared" si="1"/>
         <v>228181.03</v>
       </c>
-      <c r="M13" s="130">
+      <c r="N13" s="128">
         <f t="shared" si="2"/>
         <v>235026.03</v>
       </c>
-      <c r="N13" s="34">
-        <f t="shared" ref="N13:N35" si="6">N12+0.01</f>
+      <c r="O13" s="33">
+        <f t="shared" ref="O13:O35" si="6">O12+0.01</f>
         <v>0.03</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="122" t="s">
+      <c r="P13" s="32"/>
+    </row>
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="120" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="122" t="s">
+      <c r="B14" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="122" t="s">
+      <c r="C14" s="120" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="122"/>
-      <c r="E14" s="143">
+      <c r="D14" s="120"/>
+      <c r="E14" s="141">
         <v>4.33</v>
       </c>
-      <c r="F14" s="124">
+      <c r="F14" s="122">
         <v>198819</v>
       </c>
-      <c r="G14" s="125"/>
-      <c r="H14" s="126">
+      <c r="G14" s="123"/>
+      <c r="H14" s="123"/>
+      <c r="I14" s="124">
         <f t="shared" si="0"/>
         <v>198819</v>
       </c>
-      <c r="I14" s="126">
+      <c r="J14" s="124">
         <f t="shared" si="3"/>
         <v>5964.57</v>
       </c>
-      <c r="J14" s="127">
+      <c r="K14" s="125">
         <f t="shared" si="4"/>
         <v>164540</v>
       </c>
-      <c r="K14" s="128">
+      <c r="L14" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L14" s="129">
+      <c r="M14" s="127">
         <f t="shared" si="1"/>
         <v>369324.04</v>
       </c>
-      <c r="M14" s="130">
+      <c r="N14" s="128">
         <f t="shared" si="2"/>
         <v>380404.04</v>
       </c>
-      <c r="N14" s="34">
+      <c r="O14" s="33">
         <f t="shared" si="6"/>
         <v>0.04</v>
       </c>
-      <c r="P14" s="34"/>
-    </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="122" t="s">
+      <c r="Q14" s="33"/>
+    </row>
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="122" t="s">
+      <c r="B15" s="120" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="122" t="s">
+      <c r="C15" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="122" t="s">
+      <c r="D15" s="120" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="143">
+      <c r="E15" s="141">
         <v>6.18</v>
       </c>
-      <c r="F15" s="124">
+      <c r="F15" s="122">
         <v>283765</v>
       </c>
-      <c r="G15" s="125">
+      <c r="G15" s="123">
         <f>F15</f>
         <v>283765</v>
       </c>
-      <c r="H15" s="126">
+      <c r="H15" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="126">
+      <c r="J15" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J15" s="127">
+      <c r="K15" s="125">
         <f t="shared" si="4"/>
         <v>234840</v>
       </c>
-      <c r="K15" s="128">
+      <c r="L15" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L15" s="129">
+      <c r="M15" s="127">
         <f t="shared" si="1"/>
         <v>234840.05</v>
       </c>
-      <c r="M15" s="130">
+      <c r="N15" s="128">
         <f t="shared" si="2"/>
         <v>241885.05</v>
       </c>
-      <c r="N15" s="34">
+      <c r="O15" s="33">
         <f t="shared" si="6"/>
         <v>0.05</v>
       </c>
-      <c r="P15" s="34"/>
-    </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="122" t="s">
+      <c r="Q15" s="33"/>
+    </row>
+    <row r="16" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="122" t="s">
+      <c r="B16" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="122" t="s">
+      <c r="C16" s="120" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="122"/>
-      <c r="E16" s="143">
+      <c r="D16" s="120"/>
+      <c r="E16" s="141">
         <v>4.33</v>
       </c>
-      <c r="F16" s="124">
+      <c r="F16" s="122">
         <v>198806</v>
       </c>
-      <c r="G16" s="125">
+      <c r="G16" s="123">
         <f>F16</f>
         <v>198806</v>
       </c>
-      <c r="H16" s="126">
+      <c r="H16" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="126">
+      <c r="J16" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J16" s="127">
+      <c r="K16" s="125">
         <f t="shared" si="4"/>
         <v>164540</v>
       </c>
-      <c r="K16" s="128">
+      <c r="L16" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L16" s="129">
+      <c r="M16" s="127">
         <f t="shared" si="1"/>
         <v>164540.06</v>
       </c>
-      <c r="M16" s="130">
+      <c r="N16" s="128">
         <f t="shared" si="2"/>
         <v>169476.06</v>
       </c>
-      <c r="N16" s="34">
+      <c r="O16" s="33">
         <f t="shared" si="6"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="122" t="s">
+    <row r="17" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="122" t="s">
+      <c r="B17" s="120" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="122" t="s">
+      <c r="C17" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="122"/>
-      <c r="E17" s="143">
+      <c r="D17" s="120"/>
+      <c r="E17" s="141">
         <v>6.18</v>
       </c>
-      <c r="F17" s="124">
+      <c r="F17" s="122">
         <v>285791</v>
       </c>
-      <c r="G17" s="125">
+      <c r="G17" s="123">
         <f>320000-G32</f>
         <v>284515.59999999998</v>
       </c>
-      <c r="H17" s="126">
+      <c r="H17" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I17" s="124">
         <f t="shared" si="0"/>
         <v>1275.4000000000233</v>
       </c>
-      <c r="I17" s="126">
+      <c r="J17" s="124">
         <f t="shared" si="3"/>
         <v>38.262000000000697</v>
       </c>
-      <c r="J17" s="127">
+      <c r="K17" s="125">
         <f t="shared" si="4"/>
         <v>234840</v>
       </c>
-      <c r="K17" s="128">
+      <c r="L17" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L17" s="129">
+      <c r="M17" s="127">
         <f t="shared" si="1"/>
         <v>236154.07</v>
       </c>
-      <c r="M17" s="130">
+      <c r="N17" s="128">
         <f t="shared" si="2"/>
         <v>243239.07</v>
       </c>
-      <c r="N17" s="34">
+      <c r="O17" s="33">
         <f t="shared" si="6"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="122" t="s">
+    <row r="18" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="120" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="122" t="s">
+      <c r="B18" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="122" t="s">
+      <c r="C18" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="122"/>
-      <c r="E18" s="143">
+      <c r="D18" s="120"/>
+      <c r="E18" s="141">
         <v>4.33</v>
       </c>
-      <c r="F18" s="124">
+      <c r="F18" s="122">
         <v>198819</v>
       </c>
-      <c r="G18" s="125">
+      <c r="G18" s="123">
         <f>F18</f>
         <v>198819</v>
       </c>
-      <c r="H18" s="126">
+      <c r="H18" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="126">
+      <c r="J18" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J18" s="127">
+      <c r="K18" s="125">
         <f t="shared" si="4"/>
         <v>164540</v>
       </c>
-      <c r="K18" s="128">
+      <c r="L18" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L18" s="129">
+      <c r="M18" s="127">
         <f t="shared" si="1"/>
         <v>164540.07999999999</v>
       </c>
-      <c r="M18" s="130">
+      <c r="N18" s="128">
         <f t="shared" si="2"/>
         <v>169476.08</v>
       </c>
-      <c r="N18" s="34">
+      <c r="O18" s="33">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="122" t="s">
+    <row r="19" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="122" t="s">
+      <c r="B19" s="120" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="122" t="s">
+      <c r="C19" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="122"/>
-      <c r="E19" s="143">
+      <c r="D19" s="120"/>
+      <c r="E19" s="141">
         <v>6.18</v>
       </c>
-      <c r="F19" s="124">
+      <c r="F19" s="122">
         <v>284765</v>
       </c>
-      <c r="G19" s="125"/>
-      <c r="H19" s="126">
+      <c r="G19" s="123">
+        <f>F19</f>
+        <v>284765</v>
+      </c>
+      <c r="H19" s="123" t="s">
+        <v>130</v>
+      </c>
+      <c r="I19" s="124">
         <f t="shared" si="0"/>
-        <v>284765</v>
-      </c>
-      <c r="I19" s="126">
+        <v>0</v>
+      </c>
+      <c r="J19" s="124">
         <f t="shared" si="3"/>
-        <v>8542.9499999999989</v>
-      </c>
-      <c r="J19" s="127">
+        <v>0</v>
+      </c>
+      <c r="K19" s="125">
         <f t="shared" si="4"/>
         <v>234840</v>
       </c>
-      <c r="K19" s="128">
+      <c r="L19" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L19" s="129">
+      <c r="M19" s="127">
         <f t="shared" si="1"/>
-        <v>528148.09</v>
-      </c>
-      <c r="M19" s="130">
+        <v>234840.09</v>
+      </c>
+      <c r="N19" s="128">
         <f t="shared" si="2"/>
-        <v>543992.09</v>
-      </c>
-      <c r="N19" s="34">
+        <v>241885.09</v>
+      </c>
+      <c r="O19" s="33">
         <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="122" t="s">
+    <row r="20" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="122" t="s">
+      <c r="B20" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="122" t="s">
+      <c r="C20" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="122"/>
-      <c r="E20" s="143">
+      <c r="D20" s="120"/>
+      <c r="E20" s="141">
         <v>4.33</v>
       </c>
-      <c r="F20" s="124">
+      <c r="F20" s="122">
         <v>198858</v>
       </c>
-      <c r="G20" s="125"/>
-      <c r="H20" s="126">
+      <c r="G20" s="123">
+        <f>F20</f>
+        <v>198858</v>
+      </c>
+      <c r="H20" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20" s="124">
         <f t="shared" si="0"/>
-        <v>198858</v>
-      </c>
-      <c r="I20" s="126">
+        <v>0</v>
+      </c>
+      <c r="J20" s="124">
         <f t="shared" si="3"/>
-        <v>5965.74</v>
-      </c>
-      <c r="J20" s="127">
+        <v>0</v>
+      </c>
+      <c r="K20" s="125">
         <f t="shared" si="4"/>
         <v>164540</v>
       </c>
-      <c r="K20" s="128">
+      <c r="L20" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L20" s="129">
+      <c r="M20" s="127">
         <f t="shared" si="1"/>
-        <v>369364.1</v>
-      </c>
-      <c r="M20" s="130">
+        <v>164540.1</v>
+      </c>
+      <c r="N20" s="128">
         <f t="shared" si="2"/>
-        <v>380445.1</v>
-      </c>
-      <c r="N20" s="34">
+        <v>169476.1</v>
+      </c>
+      <c r="O20" s="33">
         <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="122" t="s">
+    <row r="21" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="B21" s="122" t="s">
+      <c r="B21" s="120" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="122" t="s">
+      <c r="C21" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="122" t="s">
+      <c r="D21" s="120" t="s">
         <v>118</v>
       </c>
-      <c r="E21" s="143">
+      <c r="E21" s="141">
         <v>6.18</v>
       </c>
-      <c r="F21" s="124">
+      <c r="F21" s="122">
         <v>283765</v>
       </c>
-      <c r="G21" s="125">
+      <c r="G21" s="123">
         <f>F21</f>
         <v>283765</v>
       </c>
-      <c r="H21" s="126">
+      <c r="H21" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21" s="126">
+      <c r="J21" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J21" s="127">
+      <c r="K21" s="125">
         <f t="shared" si="4"/>
         <v>234840</v>
       </c>
-      <c r="K21" s="128">
+      <c r="L21" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L21" s="129">
+      <c r="M21" s="127">
         <f t="shared" si="1"/>
         <v>234840.11</v>
       </c>
-      <c r="M21" s="130">
+      <c r="N21" s="128">
         <f t="shared" si="2"/>
         <v>241885.11</v>
       </c>
-      <c r="N21" s="34">
+      <c r="O21" s="33">
         <f t="shared" si="6"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="122" t="s">
+    <row r="22" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="122" t="s">
+      <c r="B22" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="122" t="s">
+      <c r="C22" s="120" t="s">
         <v>75</v>
       </c>
-      <c r="D22" s="122"/>
-      <c r="E22" s="143">
+      <c r="D22" s="120"/>
+      <c r="E22" s="141">
         <v>4.33</v>
       </c>
-      <c r="F22" s="124">
+      <c r="F22" s="122">
         <v>198788</v>
       </c>
-      <c r="G22" s="125"/>
-      <c r="H22" s="126">
+      <c r="G22" s="123">
+        <f>F22</f>
+        <v>198788</v>
+      </c>
+      <c r="H22" s="123" t="s">
+        <v>130</v>
+      </c>
+      <c r="I22" s="124">
         <f t="shared" si="0"/>
-        <v>198788</v>
-      </c>
-      <c r="I22" s="126">
+        <v>0</v>
+      </c>
+      <c r="J22" s="124">
         <f t="shared" si="3"/>
-        <v>5963.6399999999994</v>
-      </c>
-      <c r="J22" s="127">
+        <v>0</v>
+      </c>
+      <c r="K22" s="125">
         <f t="shared" si="4"/>
         <v>164540</v>
       </c>
-      <c r="K22" s="128">
+      <c r="L22" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L22" s="129">
+      <c r="M22" s="127">
         <f t="shared" si="1"/>
-        <v>369292.12</v>
-      </c>
-      <c r="M22" s="130">
+        <v>164540.12</v>
+      </c>
+      <c r="N22" s="128">
         <f t="shared" si="2"/>
-        <v>380371.12</v>
-      </c>
-      <c r="N22" s="34">
+        <v>169476.12</v>
+      </c>
+      <c r="O22" s="33">
         <f t="shared" si="6"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="122" t="s">
+    <row r="23" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="122" t="s">
+      <c r="B23" s="120" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="122" t="s">
+      <c r="C23" s="120" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="122" t="s">
+      <c r="D23" s="120" t="s">
         <v>123</v>
       </c>
-      <c r="E23" s="143">
+      <c r="E23" s="141">
         <v>6.18</v>
       </c>
-      <c r="F23" s="124">
+      <c r="F23" s="122">
         <v>283767</v>
       </c>
-      <c r="G23" s="125">
+      <c r="G23" s="123">
         <f>319251.4-G31</f>
         <v>283767</v>
       </c>
-      <c r="H23" s="126">
+      <c r="H23" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I23" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I23" s="126">
+      <c r="J23" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J23" s="127">
+      <c r="K23" s="125">
         <f t="shared" si="4"/>
         <v>234840</v>
       </c>
-      <c r="K23" s="128">
+      <c r="L23" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L23" s="129">
+      <c r="M23" s="127">
         <f t="shared" si="1"/>
         <v>234840.13</v>
       </c>
-      <c r="M23" s="130">
+      <c r="N23" s="128">
         <f t="shared" si="2"/>
         <v>241885.13</v>
       </c>
-      <c r="N23" s="34">
+      <c r="O23" s="33">
         <f t="shared" si="6"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="122" t="s">
+    <row r="24" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="120" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="122" t="s">
+      <c r="B24" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="122" t="s">
+      <c r="C24" s="120" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="122"/>
-      <c r="E24" s="143">
+      <c r="D24" s="120"/>
+      <c r="E24" s="141">
         <v>4.33</v>
       </c>
-      <c r="F24" s="124">
+      <c r="F24" s="122">
         <v>198819</v>
       </c>
-      <c r="G24" s="125"/>
-      <c r="H24" s="126">
+      <c r="G24" s="123">
+        <f>F24</f>
+        <v>198819</v>
+      </c>
+      <c r="H24" s="123"/>
+      <c r="I24" s="124">
         <f t="shared" si="0"/>
-        <v>198819</v>
-      </c>
-      <c r="I24" s="126">
+        <v>0</v>
+      </c>
+      <c r="J24" s="124">
         <f t="shared" si="3"/>
-        <v>5964.57</v>
-      </c>
-      <c r="J24" s="127">
+        <v>0</v>
+      </c>
+      <c r="K24" s="125">
         <f t="shared" si="4"/>
         <v>164540</v>
       </c>
-      <c r="K24" s="128">
+      <c r="L24" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L24" s="129">
+      <c r="M24" s="127">
         <f t="shared" si="1"/>
-        <v>369324.14</v>
-      </c>
-      <c r="M24" s="130">
+        <v>164540.14000000001</v>
+      </c>
+      <c r="N24" s="128">
         <f t="shared" si="2"/>
-        <v>380404.14</v>
-      </c>
-      <c r="N24" s="34">
+        <v>169476.14</v>
+      </c>
+      <c r="O24" s="33">
         <f t="shared" si="6"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="131" t="s">
+    <row r="25" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="129" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="131" t="s">
+      <c r="B25" s="129" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="131" t="s">
+      <c r="C25" s="129" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="131"/>
-      <c r="E25" s="144">
+      <c r="D25" s="129"/>
+      <c r="E25" s="142">
         <v>6.18</v>
       </c>
-      <c r="F25" s="132">
+      <c r="F25" s="130">
         <v>283765</v>
       </c>
-      <c r="G25" s="125">
+      <c r="G25" s="123">
         <f>518068-G26-G35</f>
         <v>283764.59999999998</v>
       </c>
-      <c r="H25" s="126">
+      <c r="H25" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I25" s="124">
         <f t="shared" si="0"/>
         <v>0.40000000002328306</v>
       </c>
-      <c r="I25" s="126">
+      <c r="J25" s="124">
         <f t="shared" si="3"/>
         <v>1.2000000000698492E-2</v>
       </c>
-      <c r="J25" s="127">
+      <c r="K25" s="125">
         <f t="shared" si="4"/>
         <v>234840</v>
       </c>
-      <c r="K25" s="128">
+      <c r="L25" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L25" s="129">
+      <c r="M25" s="127">
         <f t="shared" si="1"/>
         <v>234840.15</v>
       </c>
-      <c r="M25" s="130">
+      <c r="N25" s="128">
         <f t="shared" si="2"/>
         <v>241885.15</v>
       </c>
-      <c r="N25" s="34">
+      <c r="O25" s="33">
         <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="122" t="s">
+    <row r="26" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="122" t="s">
+      <c r="B26" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="122" t="s">
+      <c r="C26" s="120" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="122"/>
-      <c r="E26" s="143">
+      <c r="D26" s="120"/>
+      <c r="E26" s="141">
         <v>4.33</v>
       </c>
-      <c r="F26" s="124">
+      <c r="F26" s="122">
         <v>198819</v>
       </c>
-      <c r="G26" s="125">
+      <c r="G26" s="123">
         <f>F26</f>
         <v>198819</v>
       </c>
-      <c r="H26" s="126">
+      <c r="H26" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I26" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="126">
+      <c r="J26" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="127">
+      <c r="K26" s="125">
         <f t="shared" si="4"/>
         <v>164540</v>
       </c>
-      <c r="K26" s="128">
+      <c r="L26" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L26" s="129">
+      <c r="M26" s="127">
         <f t="shared" si="1"/>
         <v>164540.16</v>
       </c>
-      <c r="M26" s="130">
+      <c r="N26" s="128">
         <f t="shared" si="2"/>
         <v>169476.16</v>
       </c>
-      <c r="N26" s="34">
+      <c r="O26" s="33">
         <f t="shared" si="6"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="122" t="s">
+    <row r="27" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="120" t="s">
         <v>81</v>
       </c>
-      <c r="B27" s="122" t="s">
+      <c r="B27" s="120" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="122" t="s">
+      <c r="C27" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="D27" s="122" t="s">
+      <c r="D27" s="120" t="s">
         <v>121</v>
       </c>
-      <c r="E27" s="143">
+      <c r="E27" s="141">
         <v>6.18</v>
       </c>
-      <c r="F27" s="132">
+      <c r="F27" s="130">
         <v>281323</v>
       </c>
-      <c r="G27" s="125">
+      <c r="G27" s="123">
         <f>320000-G29</f>
         <v>284515.59999999998</v>
       </c>
-      <c r="H27" s="126">
+      <c r="H27" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="124">
         <f t="shared" si="0"/>
         <v>-3192.5999999999767</v>
       </c>
-      <c r="I27" s="126">
+      <c r="J27" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J27" s="127">
+      <c r="K27" s="125">
         <f t="shared" si="4"/>
         <v>234840</v>
       </c>
-      <c r="K27" s="128">
+      <c r="L27" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L27" s="129">
+      <c r="M27" s="127">
         <f t="shared" si="1"/>
         <v>231647.17</v>
       </c>
-      <c r="M27" s="130">
+      <c r="N27" s="128">
         <f t="shared" si="2"/>
         <v>238596.17</v>
       </c>
-      <c r="N27" s="34">
+      <c r="O27" s="33">
         <f t="shared" si="6"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="122" t="s">
+    <row r="28" spans="1:15" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="120" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="122" t="s">
+      <c r="B28" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="122" t="s">
+      <c r="C28" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="D28" s="122"/>
-      <c r="E28" s="143">
+      <c r="D28" s="120"/>
+      <c r="E28" s="141">
         <v>4.33</v>
       </c>
-      <c r="F28" s="124">
+      <c r="F28" s="122">
         <v>198819</v>
       </c>
-      <c r="G28" s="125"/>
-      <c r="H28" s="126">
+      <c r="G28" s="123">
+        <f t="shared" ref="G28:G33" si="7">F28</f>
+        <v>198819</v>
+      </c>
+      <c r="H28" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I28" s="124">
         <f t="shared" si="0"/>
-        <v>198819</v>
-      </c>
-      <c r="I28" s="126">
+        <v>0</v>
+      </c>
+      <c r="J28" s="124">
         <f t="shared" si="3"/>
-        <v>5964.57</v>
-      </c>
-      <c r="J28" s="127">
+        <v>0</v>
+      </c>
+      <c r="K28" s="125">
         <f t="shared" si="4"/>
         <v>164540</v>
       </c>
-      <c r="K28" s="128">
+      <c r="L28" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L28" s="129">
+      <c r="M28" s="127">
         <f t="shared" si="1"/>
-        <v>369324.18</v>
-      </c>
-      <c r="M28" s="130">
+        <v>164540.18</v>
+      </c>
+      <c r="N28" s="128">
         <f t="shared" si="2"/>
-        <v>380404.18</v>
-      </c>
-      <c r="N28" s="34">
+        <v>169476.18</v>
+      </c>
+      <c r="O28" s="33">
         <f t="shared" si="6"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="170" t="s">
+    <row r="29" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="200" t="s">
         <v>85</v>
       </c>
-      <c r="B29" s="171"/>
-      <c r="C29" s="122" t="s">
+      <c r="B29" s="201"/>
+      <c r="C29" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="122"/>
-      <c r="E29" s="143">
+      <c r="D29" s="120"/>
+      <c r="E29" s="141">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F29" s="124">
+      <c r="F29" s="122">
         <v>35484.400000000001</v>
       </c>
-      <c r="G29" s="133">
-        <f>F29</f>
+      <c r="G29" s="131">
+        <f t="shared" si="7"/>
         <v>35484.400000000001</v>
       </c>
-      <c r="H29" s="126">
+      <c r="H29" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I29" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I29" s="126">
+      <c r="J29" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="127">
+      <c r="K29" s="125">
         <f t="shared" si="4"/>
         <v>29374</v>
       </c>
-      <c r="K29" s="128">
+      <c r="L29" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L29" s="129">
+      <c r="M29" s="127">
         <f t="shared" si="1"/>
         <v>29374.19</v>
       </c>
-      <c r="M29" s="130">
+      <c r="N29" s="128">
         <f t="shared" si="2"/>
         <v>30255.19</v>
       </c>
-      <c r="N29" s="34">
+      <c r="O29" s="33">
         <f t="shared" si="6"/>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="170" t="s">
+    <row r="30" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="200" t="s">
         <v>86</v>
       </c>
-      <c r="B30" s="171"/>
-      <c r="C30" s="131" t="s">
+      <c r="B30" s="201"/>
+      <c r="C30" s="129" t="s">
         <v>62</v>
       </c>
-      <c r="D30" s="122"/>
-      <c r="E30" s="143">
+      <c r="D30" s="120"/>
+      <c r="E30" s="141">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F30" s="134">
+      <c r="F30" s="132">
         <v>35484.400000000001</v>
       </c>
-      <c r="G30" s="135">
-        <f>F30</f>
+      <c r="G30" s="133">
+        <f t="shared" si="7"/>
         <v>35484.400000000001</v>
       </c>
-      <c r="H30" s="126">
+      <c r="H30" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I30" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="126">
+      <c r="J30" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="127">
+      <c r="K30" s="125">
         <f t="shared" si="4"/>
         <v>29374</v>
       </c>
-      <c r="K30" s="128">
+      <c r="L30" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L30" s="129">
+      <c r="M30" s="127">
         <f t="shared" si="1"/>
         <v>29374.2</v>
       </c>
-      <c r="M30" s="130">
+      <c r="N30" s="128">
         <f t="shared" si="2"/>
         <v>30255.200000000001</v>
       </c>
-      <c r="N30" s="34">
+      <c r="O30" s="33">
         <f t="shared" si="6"/>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="170" t="s">
+    <row r="31" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="200" t="s">
         <v>87</v>
       </c>
-      <c r="B31" s="171"/>
-      <c r="C31" s="136" t="s">
+      <c r="B31" s="201"/>
+      <c r="C31" s="134" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="122" t="s">
+      <c r="D31" s="120" t="s">
         <v>123</v>
       </c>
-      <c r="E31" s="143">
+      <c r="E31" s="141">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F31" s="134">
+      <c r="F31" s="132">
         <v>35484.400000000001</v>
       </c>
-      <c r="G31" s="135">
-        <f>F31</f>
+      <c r="G31" s="133">
+        <f t="shared" si="7"/>
         <v>35484.400000000001</v>
       </c>
-      <c r="H31" s="126">
+      <c r="H31" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I31" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="126">
+      <c r="J31" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="127">
+      <c r="K31" s="125">
         <f t="shared" si="4"/>
         <v>29374</v>
       </c>
-      <c r="K31" s="128">
+      <c r="L31" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L31" s="129">
+      <c r="M31" s="127">
         <f t="shared" si="1"/>
         <v>29374.21</v>
       </c>
-      <c r="M31" s="130">
+      <c r="N31" s="128">
         <f t="shared" si="2"/>
         <v>30255.21</v>
       </c>
-      <c r="N31" s="34">
+      <c r="O31" s="33">
         <f t="shared" si="6"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="170" t="s">
+    <row r="32" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="200" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="171"/>
-      <c r="C32" s="122" t="s">
+      <c r="B32" s="201"/>
+      <c r="C32" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="122"/>
-      <c r="E32" s="143">
+      <c r="D32" s="120"/>
+      <c r="E32" s="141">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F32" s="134">
+      <c r="F32" s="132">
         <v>35484.400000000001</v>
       </c>
-      <c r="G32" s="135">
-        <f>F32</f>
+      <c r="G32" s="133">
+        <f t="shared" si="7"/>
         <v>35484.400000000001</v>
       </c>
-      <c r="H32" s="126">
+      <c r="H32" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I32" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I32" s="126">
+      <c r="J32" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J32" s="127">
+      <c r="K32" s="125">
         <f t="shared" si="4"/>
         <v>29374</v>
       </c>
-      <c r="K32" s="128">
+      <c r="L32" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L32" s="129">
+      <c r="M32" s="127">
         <f t="shared" si="1"/>
         <v>29374.22</v>
       </c>
-      <c r="M32" s="130">
+      <c r="N32" s="128">
         <f t="shared" si="2"/>
         <v>30255.22</v>
       </c>
-      <c r="N32" s="34">
+      <c r="O32" s="33">
         <f t="shared" si="6"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="170" t="s">
+    <row r="33" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="200" t="s">
         <v>89</v>
       </c>
-      <c r="B33" s="171"/>
-      <c r="C33" s="137" t="s">
+      <c r="B33" s="201"/>
+      <c r="C33" s="135" t="s">
         <v>71</v>
       </c>
-      <c r="D33" s="137"/>
-      <c r="E33" s="143">
+      <c r="D33" s="135"/>
+      <c r="E33" s="141">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F33" s="134">
+      <c r="F33" s="132">
         <v>35484.400000000001</v>
       </c>
-      <c r="G33" s="135"/>
-      <c r="H33" s="126">
+      <c r="G33" s="133">
+        <f t="shared" si="7"/>
+        <v>35484.400000000001</v>
+      </c>
+      <c r="H33" s="133" t="s">
+        <v>130</v>
+      </c>
+      <c r="I33" s="124">
         <f t="shared" si="0"/>
-        <v>35484.400000000001</v>
-      </c>
-      <c r="I33" s="126">
+        <v>0</v>
+      </c>
+      <c r="J33" s="124">
         <f t="shared" si="3"/>
-        <v>1064.5319999999999</v>
-      </c>
-      <c r="J33" s="127">
+        <v>0</v>
+      </c>
+      <c r="K33" s="125">
         <f t="shared" si="4"/>
         <v>29374</v>
       </c>
-      <c r="K33" s="128">
+      <c r="L33" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L33" s="129">
+      <c r="M33" s="127">
         <f t="shared" si="1"/>
-        <v>65923.23</v>
-      </c>
-      <c r="M33" s="130">
+        <v>29374.23</v>
+      </c>
+      <c r="N33" s="128">
         <f t="shared" si="2"/>
-        <v>67901.23</v>
-      </c>
-      <c r="N33" s="34">
+        <v>30255.23</v>
+      </c>
+      <c r="O33" s="33">
         <f t="shared" si="6"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="170" t="s">
+    <row r="34" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="200" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="171"/>
-      <c r="C34" s="137" t="s">
+      <c r="B34" s="201"/>
+      <c r="C34" s="135" t="s">
         <v>74</v>
       </c>
-      <c r="D34" s="137"/>
-      <c r="E34" s="143">
+      <c r="D34" s="135"/>
+      <c r="E34" s="141">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F34" s="134">
+      <c r="F34" s="132">
         <v>34163.4</v>
       </c>
-      <c r="G34" s="135"/>
-      <c r="H34" s="126">
+      <c r="G34" s="133"/>
+      <c r="H34" s="133"/>
+      <c r="I34" s="124">
         <f t="shared" si="0"/>
         <v>34163.4</v>
       </c>
-      <c r="I34" s="126">
+      <c r="J34" s="124">
         <f t="shared" si="3"/>
         <v>1024.902</v>
       </c>
-      <c r="J34" s="127">
+      <c r="K34" s="125">
         <f t="shared" si="4"/>
         <v>29374</v>
       </c>
-      <c r="K34" s="128">
+      <c r="L34" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L34" s="129">
+      <c r="M34" s="127">
         <f t="shared" si="1"/>
         <v>64562.239999999998</v>
       </c>
-      <c r="M34" s="130">
+      <c r="N34" s="128">
         <f t="shared" si="2"/>
         <v>66499.239999999991</v>
       </c>
-      <c r="N34" s="34">
+      <c r="O34" s="33">
         <f t="shared" si="6"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="170" t="s">
+    <row r="35" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="200" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="171"/>
-      <c r="C35" s="137" t="s">
+      <c r="B35" s="201"/>
+      <c r="C35" s="135" t="s">
         <v>80</v>
       </c>
-      <c r="D35" s="137"/>
-      <c r="E35" s="123">
+      <c r="D35" s="135"/>
+      <c r="E35" s="121">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F35" s="134">
+      <c r="F35" s="132">
         <v>35484.400000000001</v>
       </c>
-      <c r="G35" s="125">
+      <c r="G35" s="123">
         <f>F35</f>
         <v>35484.400000000001</v>
       </c>
-      <c r="H35" s="126">
+      <c r="H35" s="123" t="s">
+        <v>59</v>
+      </c>
+      <c r="I35" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I35" s="126">
+      <c r="J35" s="124">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="127">
+      <c r="K35" s="125">
         <f t="shared" si="4"/>
         <v>29374</v>
       </c>
-      <c r="K35" s="128">
+      <c r="L35" s="126">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L35" s="129">
+      <c r="M35" s="127">
         <f t="shared" si="1"/>
         <v>29374.25</v>
       </c>
-      <c r="M35" s="130">
+      <c r="N35" s="128">
         <f t="shared" si="2"/>
         <v>30255.25</v>
       </c>
-      <c r="N35" s="34">
+      <c r="O35" s="33">
         <f t="shared" si="6"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="192" t="s">
+    <row r="36" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="202" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="192"/>
-      <c r="C36" s="193"/>
-      <c r="D36" s="147"/>
-      <c r="E36" s="138">
-        <f t="shared" ref="E36:K36" si="7">SUM(E11:E35)</f>
+      <c r="B36" s="202"/>
+      <c r="C36" s="203"/>
+      <c r="D36" s="145"/>
+      <c r="E36" s="136">
+        <f t="shared" ref="E36:L36" si="8">SUM(E11:E35)</f>
         <v>100.00099999999993</v>
       </c>
-      <c r="F36" s="139">
-        <f t="shared" si="7"/>
+      <c r="F36" s="137">
+        <f t="shared" si="8"/>
         <v>4584998.8000000026</v>
       </c>
-      <c r="G36" s="140">
-        <f t="shared" si="7"/>
-        <v>2961293.3999999994</v>
-      </c>
-      <c r="H36" s="140">
-        <f t="shared" si="7"/>
-        <v>1623705.4</v>
-      </c>
-      <c r="I36" s="141">
-        <f t="shared" si="7"/>
-        <v>49006.697999999997</v>
-      </c>
-      <c r="J36" s="141">
-        <f t="shared" si="7"/>
+      <c r="G36" s="138">
+        <f t="shared" si="8"/>
+        <v>4360591.8000000017</v>
+      </c>
+      <c r="H36" s="138"/>
+      <c r="I36" s="138">
+        <f t="shared" si="8"/>
+        <v>224407.00000000009</v>
+      </c>
+      <c r="J36" s="139">
+        <f t="shared" si="8"/>
+        <v>7027.746000000001</v>
+      </c>
+      <c r="K36" s="139">
+        <f t="shared" si="8"/>
         <v>3800038</v>
       </c>
-      <c r="K36" s="140">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L36" s="142">
-        <f>SUM(L11:L28)</f>
-        <v>5195397.71</v>
-      </c>
-      <c r="M36" s="142">
-        <f>SUM(M11:M35)</f>
-        <v>5636935.2500000009</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="194"/>
-      <c r="B38" s="194"/>
-      <c r="E38" s="195"/>
-      <c r="F38" s="196"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="194"/>
-      <c r="B39" s="194"/>
-      <c r="E39" s="195"/>
-      <c r="F39" s="196"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="L36" s="138">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="140">
+        <f>SUM(M11:M28)</f>
+        <v>3790667.7100000004</v>
+      </c>
+      <c r="N36" s="140">
+        <f>SUM(N11:N35)</f>
+        <v>4152415.2500000009</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="F37" t="s">
+        <v>132</v>
+      </c>
+      <c r="G37" s="155">
+        <f>SUMIF(H11:H35,"B",G11:G35)</f>
+        <v>3642735.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="204"/>
+      <c r="B38" s="204"/>
+      <c r="E38" s="205"/>
+      <c r="F38" s="206" t="s">
+        <v>133</v>
+      </c>
+      <c r="G38" s="155">
+        <f>SUMIF(H11:H35,"E",G11:G35)</f>
+        <v>519037.4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="204"/>
+      <c r="B39" s="204"/>
+      <c r="E39" s="205"/>
+      <c r="F39" s="206"/>
+      <c r="G39" s="156">
+        <f>SUM(G37:G38)</f>
+        <v>4161772.8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F50">
         <f>SUM(E48:E49)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="F54">
         <f>SUM(E52:E53)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
+    <mergeCell ref="A38:B39"/>
     <mergeCell ref="E38:E39"/>
     <mergeCell ref="F38:F39"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="G2:I2"/>
     <mergeCell ref="D2:E2"/>
+    <mergeCell ref="H9:H10"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A38:B39"/>
-    <mergeCell ref="E1:L1"/>
-    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="E1:M1"/>
+    <mergeCell ref="J9:J10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="I9:I10"/>
     <mergeCell ref="K9:K10"/>
-    <mergeCell ref="A4:M8"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="A4:N8"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="N9:N10"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/2DE MAYO/FEBRERO/2DEDMAYO-Febrero.xlsx
+++ b/2026/2DE MAYO/FEBRERO/2DEDMAYO-Febrero.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\2DE MAYO\FEBRERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6039587C-E2FD-407B-8A88-E273655C38E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBA015E-1349-40A6-848B-646874275CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="136">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1419,6 +1419,12 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1476,71 +1482,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1550,27 +1511,66 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1952,11 +1952,11 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
-      <c r="B1" s="163" t="s">
+      <c r="B1" s="167" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
       <c r="E1" s="51"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1970,12 +1970,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
-      <c r="B3" s="170" t="s">
+      <c r="B3" s="174" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="170"/>
-      <c r="D3" s="170"/>
-      <c r="E3" s="171"/>
+      <c r="C3" s="174"/>
+      <c r="D3" s="174"/>
+      <c r="E3" s="175"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
@@ -2013,49 +2013,49 @@
       <c r="E6" s="20"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="173" t="s">
+      <c r="B8" s="177" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="173"/>
+      <c r="C8" s="177"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="173"/>
-      <c r="C9" s="173"/>
+      <c r="B9" s="177"/>
+      <c r="C9" s="177"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="173"/>
-      <c r="C10" s="173"/>
+      <c r="B10" s="177"/>
+      <c r="C10" s="177"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="172" t="s">
+      <c r="A13" s="176" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="172"/>
-      <c r="C13" s="172"/>
-      <c r="D13" s="172"/>
-      <c r="E13" s="172"/>
+      <c r="B13" s="176"/>
+      <c r="C13" s="176"/>
+      <c r="D13" s="176"/>
+      <c r="E13" s="176"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="172"/>
-      <c r="B14" s="172"/>
-      <c r="C14" s="172"/>
-      <c r="D14" s="172"/>
-      <c r="E14" s="172"/>
+      <c r="A14" s="176"/>
+      <c r="B14" s="176"/>
+      <c r="C14" s="176"/>
+      <c r="D14" s="176"/>
+      <c r="E14" s="176"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="172"/>
-      <c r="B15" s="172"/>
-      <c r="C15" s="172"/>
-      <c r="D15" s="172"/>
-      <c r="E15" s="172"/>
+      <c r="A15" s="176"/>
+      <c r="B15" s="176"/>
+      <c r="C15" s="176"/>
+      <c r="D15" s="176"/>
+      <c r="E15" s="176"/>
     </row>
     <row r="16" spans="1:5" ht="127.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="172"/>
-      <c r="B16" s="172"/>
-      <c r="C16" s="172"/>
-      <c r="D16" s="172"/>
-      <c r="E16" s="172"/>
+      <c r="A16" s="176"/>
+      <c r="B16" s="176"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="176"/>
+      <c r="E16" s="176"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
@@ -2081,10 +2081,10 @@
       <c r="E21" s="26"/>
     </row>
     <row r="22" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="166" t="s">
+      <c r="A22" s="170" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="167"/>
+      <c r="B22" s="171"/>
       <c r="C22" s="5"/>
       <c r="D22" s="107">
         <v>795882</v>
@@ -2207,10 +2207,10 @@
       <c r="E34" s="91"/>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="168" t="s">
+      <c r="A35" s="172" t="s">
         <v>113</v>
       </c>
-      <c r="B35" s="169"/>
+      <c r="B35" s="173"/>
       <c r="C35" s="41"/>
       <c r="D35" s="107">
         <v>35000</v>
@@ -2220,10 +2220,10 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="168" t="s">
+      <c r="A36" s="172" t="s">
         <v>111</v>
       </c>
-      <c r="B36" s="169"/>
+      <c r="B36" s="173"/>
       <c r="C36" s="41"/>
       <c r="D36" s="113">
         <v>100000</v>
@@ -2254,24 +2254,24 @@
       <c r="E38" s="94"/>
     </row>
     <row r="39" spans="1:7" s="30" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="174" t="s">
+      <c r="A39" s="178" t="s">
         <v>101</v>
       </c>
-      <c r="B39" s="175"/>
+      <c r="B39" s="179"/>
       <c r="C39" s="42"/>
-      <c r="D39" s="159">
+      <c r="D39" s="163">
         <v>60147</v>
       </c>
-      <c r="E39" s="161" t="s">
+      <c r="E39" s="165" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="176"/>
-      <c r="B40" s="177"/>
+      <c r="A40" s="180"/>
+      <c r="B40" s="181"/>
       <c r="C40" s="42"/>
-      <c r="D40" s="160"/>
-      <c r="E40" s="162"/>
+      <c r="D40" s="164"/>
+      <c r="E40" s="166"/>
     </row>
     <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="24" t="s">
@@ -2514,8 +2514,8 @@
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="117">
-        <f>1141+52473.43</f>
-        <v>53614.43</v>
+        <f>1141+52473.43+10674</f>
+        <v>64288.43</v>
       </c>
       <c r="E60" s="31"/>
     </row>
@@ -2528,7 +2528,7 @@
       <c r="D61" s="63"/>
       <c r="E61" s="58">
         <f>SUM(D59:D60)</f>
-        <v>111114.43</v>
+        <v>121788.43</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2565,7 +2565,7 @@
       <c r="D65" s="69"/>
       <c r="E65" s="70">
         <f>(SUM(E29:E63))</f>
-        <v>4481141</v>
+        <v>4491815</v>
       </c>
       <c r="F65" s="88"/>
       <c r="G65" s="33"/>
@@ -2599,22 +2599,22 @@
       <c r="E68" s="72"/>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="166"/>
-      <c r="B69" s="167"/>
+      <c r="A69" s="170"/>
+      <c r="B69" s="171"/>
       <c r="C69" s="5"/>
       <c r="D69" s="80"/>
       <c r="E69" s="59"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" s="166"/>
-      <c r="B70" s="167"/>
+      <c r="A70" s="170"/>
+      <c r="B70" s="171"/>
       <c r="C70" s="5"/>
       <c r="D70" s="61"/>
       <c r="E70" s="59"/>
     </row>
     <row r="71" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="168"/>
-      <c r="B71" s="169"/>
+      <c r="A71" s="172"/>
+      <c r="B71" s="173"/>
       <c r="C71" s="5"/>
       <c r="D71" s="61"/>
       <c r="E71" s="59"/>
@@ -2639,13 +2639,13 @@
     <row r="74" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="75" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="210" t="s">
+      <c r="A76" s="160" t="s">
         <v>19</v>
       </c>
-      <c r="B76" s="211"/>
-      <c r="C76" s="211"/>
-      <c r="D76" s="212"/>
-      <c r="E76" s="209"/>
+      <c r="B76" s="161"/>
+      <c r="C76" s="161"/>
+      <c r="D76" s="162"/>
+      <c r="E76" s="159"/>
     </row>
     <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B80" s="56">
         <f>E65</f>
-        <v>4481141</v>
+        <v>4491815</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B81" s="56">
         <f>E65-E63</f>
-        <v>3286752.87</v>
+        <v>3297426.87</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2782,7 +2782,7 @@
         <v>46</v>
       </c>
       <c r="B94" s="82">
-        <v>321565.45</v>
+        <v>133421</v>
       </c>
       <c r="C94" s="29"/>
       <c r="D94" s="36"/>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B95" s="86">
         <f>-B81</f>
-        <v>-3286752.87</v>
+        <v>-3297426.87</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B98" s="87">
         <f>PRORRATEO!G37</f>
-        <v>3642735.4</v>
+        <v>3841554.4</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="B99" s="85">
         <f>SUM(B94:C98)</f>
-        <v>677547.98</v>
+        <v>677548.5299999998</v>
       </c>
       <c r="D99" s="32"/>
       <c r="E99" s="33"/>
@@ -2840,16 +2840,16 @@
     </row>
     <row r="101" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A102" s="165" t="s">
+      <c r="A102" s="169" t="s">
         <v>27</v>
       </c>
-      <c r="B102" s="165"/>
-      <c r="C102" s="165"/>
+      <c r="B102" s="169"/>
+      <c r="C102" s="169"/>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A103" s="165"/>
-      <c r="B103" s="165"/>
-      <c r="C103" s="165"/>
+      <c r="A103" s="169"/>
+      <c r="B103" s="169"/>
+      <c r="C103" s="169"/>
     </row>
     <row r="104" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="74"/>
@@ -2879,32 +2879,32 @@
       <c r="M107" s="7"/>
     </row>
     <row r="108" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="164"/>
-      <c r="B108" s="164"/>
-      <c r="C108" s="164"/>
-      <c r="D108" s="164"/>
-      <c r="E108" s="164"/>
+      <c r="A108" s="168"/>
+      <c r="B108" s="168"/>
+      <c r="C108" s="168"/>
+      <c r="D108" s="168"/>
+      <c r="E108" s="168"/>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A109" s="164"/>
-      <c r="B109" s="164"/>
-      <c r="C109" s="164"/>
-      <c r="D109" s="164"/>
-      <c r="E109" s="164"/>
+      <c r="A109" s="168"/>
+      <c r="B109" s="168"/>
+      <c r="C109" s="168"/>
+      <c r="D109" s="168"/>
+      <c r="E109" s="168"/>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A110" s="164"/>
-      <c r="B110" s="164"/>
-      <c r="C110" s="164"/>
-      <c r="D110" s="164"/>
-      <c r="E110" s="164"/>
+      <c r="A110" s="168"/>
+      <c r="B110" s="168"/>
+      <c r="C110" s="168"/>
+      <c r="D110" s="168"/>
+      <c r="E110" s="168"/>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A111" s="164"/>
-      <c r="B111" s="164"/>
-      <c r="C111" s="164"/>
-      <c r="D111" s="164"/>
-      <c r="E111" s="164"/>
+      <c r="A111" s="168"/>
+      <c r="B111" s="168"/>
+      <c r="C111" s="168"/>
+      <c r="D111" s="168"/>
+      <c r="E111" s="168"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2941,7 +2941,7 @@
     <col min="4" max="4" width="22.33203125" customWidth="1"/>
     <col min="5" max="5" width="8.44140625" customWidth="1"/>
     <col min="6" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="0.109375" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="10.5546875" customWidth="1"/>
     <col min="10" max="10" width="9.5546875" customWidth="1"/>
     <col min="11" max="12" width="12.44140625" customWidth="1"/>
@@ -2957,15 +2957,15 @@
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
-      <c r="I1" s="178"/>
-      <c r="J1" s="178"/>
-      <c r="K1" s="178"/>
-      <c r="L1" s="178"/>
-      <c r="M1" s="178"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
+      <c r="K1" s="193"/>
+      <c r="L1" s="193"/>
+      <c r="M1" s="193"/>
       <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -2974,23 +2974,23 @@
       <c r="C2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="208">
-        <v>0</v>
-      </c>
-      <c r="E2" s="208"/>
+      <c r="D2" s="186">
+        <v>0</v>
+      </c>
+      <c r="E2" s="186"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="208"/>
-      <c r="H2" s="208"/>
-      <c r="I2" s="208"/>
+      <c r="G2" s="186"/>
+      <c r="H2" s="186"/>
+      <c r="I2" s="186"/>
       <c r="J2" s="6"/>
       <c r="K2" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="L2" s="207">
+      <c r="L2" s="185">
         <f>P2</f>
         <v>3800000</v>
       </c>
-      <c r="M2" s="207"/>
+      <c r="M2" s="185"/>
       <c r="N2" s="43"/>
       <c r="O2" s="21"/>
       <c r="P2">
@@ -3014,148 +3014,148 @@
       <c r="N3" s="46"/>
     </row>
     <row r="4" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="187" t="str">
+      <c r="A4" s="201" t="str">
         <f>RESUMEN!A13</f>
         <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
       </c>
-      <c r="B4" s="188"/>
-      <c r="C4" s="188"/>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="188"/>
-      <c r="K4" s="188"/>
-      <c r="L4" s="188"/>
-      <c r="M4" s="188"/>
-      <c r="N4" s="189"/>
+      <c r="B4" s="202"/>
+      <c r="C4" s="202"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="202"/>
+      <c r="F4" s="202"/>
+      <c r="G4" s="202"/>
+      <c r="H4" s="202"/>
+      <c r="I4" s="202"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="202"/>
+      <c r="L4" s="202"/>
+      <c r="M4" s="202"/>
+      <c r="N4" s="203"/>
     </row>
     <row r="5" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="190"/>
-      <c r="B5" s="191"/>
-      <c r="C5" s="191"/>
-      <c r="D5" s="191"/>
-      <c r="E5" s="191"/>
-      <c r="F5" s="191"/>
-      <c r="G5" s="191"/>
-      <c r="H5" s="191"/>
-      <c r="I5" s="191"/>
-      <c r="J5" s="191"/>
-      <c r="K5" s="191"/>
-      <c r="L5" s="191"/>
-      <c r="M5" s="191"/>
-      <c r="N5" s="192"/>
+      <c r="A5" s="204"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="205"/>
+      <c r="D5" s="205"/>
+      <c r="E5" s="205"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="205"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="205"/>
+      <c r="K5" s="205"/>
+      <c r="L5" s="205"/>
+      <c r="M5" s="205"/>
+      <c r="N5" s="206"/>
     </row>
     <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="190"/>
-      <c r="B6" s="191"/>
-      <c r="C6" s="191"/>
-      <c r="D6" s="191"/>
-      <c r="E6" s="191"/>
-      <c r="F6" s="191"/>
-      <c r="G6" s="191"/>
-      <c r="H6" s="191"/>
-      <c r="I6" s="191"/>
-      <c r="J6" s="191"/>
-      <c r="K6" s="191"/>
-      <c r="L6" s="191"/>
-      <c r="M6" s="191"/>
-      <c r="N6" s="192"/>
+      <c r="A6" s="204"/>
+      <c r="B6" s="205"/>
+      <c r="C6" s="205"/>
+      <c r="D6" s="205"/>
+      <c r="E6" s="205"/>
+      <c r="F6" s="205"/>
+      <c r="G6" s="205"/>
+      <c r="H6" s="205"/>
+      <c r="I6" s="205"/>
+      <c r="J6" s="205"/>
+      <c r="K6" s="205"/>
+      <c r="L6" s="205"/>
+      <c r="M6" s="205"/>
+      <c r="N6" s="206"/>
     </row>
     <row r="7" spans="1:17" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="190"/>
-      <c r="B7" s="191"/>
-      <c r="C7" s="191"/>
-      <c r="D7" s="191"/>
-      <c r="E7" s="191"/>
-      <c r="F7" s="191"/>
-      <c r="G7" s="191"/>
-      <c r="H7" s="191"/>
-      <c r="I7" s="191"/>
-      <c r="J7" s="191"/>
-      <c r="K7" s="191"/>
-      <c r="L7" s="191"/>
-      <c r="M7" s="191"/>
-      <c r="N7" s="192"/>
+      <c r="A7" s="204"/>
+      <c r="B7" s="205"/>
+      <c r="C7" s="205"/>
+      <c r="D7" s="205"/>
+      <c r="E7" s="205"/>
+      <c r="F7" s="205"/>
+      <c r="G7" s="205"/>
+      <c r="H7" s="205"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
+      <c r="L7" s="205"/>
+      <c r="M7" s="205"/>
+      <c r="N7" s="206"/>
     </row>
     <row r="8" spans="1:17" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="193"/>
-      <c r="B8" s="194"/>
-      <c r="C8" s="194"/>
-      <c r="D8" s="194"/>
-      <c r="E8" s="194"/>
-      <c r="F8" s="194"/>
-      <c r="G8" s="194"/>
-      <c r="H8" s="194"/>
-      <c r="I8" s="194"/>
-      <c r="J8" s="194"/>
-      <c r="K8" s="194"/>
-      <c r="L8" s="194"/>
-      <c r="M8" s="194"/>
-      <c r="N8" s="195"/>
+      <c r="A8" s="207"/>
+      <c r="B8" s="208"/>
+      <c r="C8" s="208"/>
+      <c r="D8" s="208"/>
+      <c r="E8" s="208"/>
+      <c r="F8" s="208"/>
+      <c r="G8" s="208"/>
+      <c r="H8" s="208"/>
+      <c r="I8" s="208"/>
+      <c r="J8" s="208"/>
+      <c r="K8" s="208"/>
+      <c r="L8" s="208"/>
+      <c r="M8" s="208"/>
+      <c r="N8" s="209"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="179" t="s">
+      <c r="A9" s="194" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="181" t="s">
+      <c r="B9" s="187" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="181" t="s">
+      <c r="C9" s="187" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="143"/>
-      <c r="E9" s="181" t="s">
+      <c r="E9" s="187" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="179" t="s">
+      <c r="F9" s="194" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="181" t="s">
+      <c r="G9" s="187" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="181" t="s">
+      <c r="H9" s="187" t="s">
         <v>129</v>
       </c>
-      <c r="I9" s="183" t="s">
+      <c r="I9" s="197" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="179" t="s">
+      <c r="J9" s="194" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="179" t="s">
+      <c r="K9" s="194" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="185" t="s">
+      <c r="L9" s="199" t="s">
         <v>53</v>
       </c>
       <c r="M9" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="N9" s="198" t="s">
+      <c r="N9" s="211" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="196"/>
-      <c r="B10" s="197"/>
-      <c r="C10" s="182"/>
+      <c r="A10" s="210"/>
+      <c r="B10" s="188"/>
+      <c r="C10" s="196"/>
       <c r="D10" s="144"/>
-      <c r="E10" s="182"/>
-      <c r="F10" s="180"/>
-      <c r="G10" s="182"/>
-      <c r="H10" s="197"/>
-      <c r="I10" s="184"/>
-      <c r="J10" s="180"/>
-      <c r="K10" s="180"/>
-      <c r="L10" s="186"/>
+      <c r="E10" s="196"/>
+      <c r="F10" s="195"/>
+      <c r="G10" s="196"/>
+      <c r="H10" s="188"/>
+      <c r="I10" s="198"/>
+      <c r="J10" s="195"/>
+      <c r="K10" s="195"/>
+      <c r="L10" s="200"/>
       <c r="M10" s="47" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/03</v>
       </c>
-      <c r="N10" s="199"/>
+      <c r="N10" s="212"/>
     </row>
     <row r="11" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="120" t="s">
@@ -3337,15 +3337,20 @@
       <c r="F14" s="122">
         <v>198819</v>
       </c>
-      <c r="G14" s="123"/>
-      <c r="H14" s="123"/>
+      <c r="G14" s="123">
+        <f>F14</f>
+        <v>198819</v>
+      </c>
+      <c r="H14" s="123" t="s">
+        <v>59</v>
+      </c>
       <c r="I14" s="124">
         <f t="shared" si="0"/>
-        <v>198819</v>
+        <v>0</v>
       </c>
       <c r="J14" s="124">
         <f t="shared" si="3"/>
-        <v>5964.57</v>
+        <v>0</v>
       </c>
       <c r="K14" s="125">
         <f t="shared" si="4"/>
@@ -3357,11 +3362,11 @@
       </c>
       <c r="M14" s="127">
         <f t="shared" si="1"/>
-        <v>369324.04</v>
+        <v>164540.04</v>
       </c>
       <c r="N14" s="128">
         <f t="shared" si="2"/>
-        <v>380404.04</v>
+        <v>169476.04</v>
       </c>
       <c r="O14" s="33">
         <f t="shared" si="6"/>
@@ -4119,10 +4124,10 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="200" t="s">
+      <c r="A29" s="189" t="s">
         <v>85</v>
       </c>
-      <c r="B29" s="201"/>
+      <c r="B29" s="190"/>
       <c r="C29" s="120" t="s">
         <v>82</v>
       </c>
@@ -4170,10 +4175,10 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="200" t="s">
+      <c r="A30" s="189" t="s">
         <v>86</v>
       </c>
-      <c r="B30" s="201"/>
+      <c r="B30" s="190"/>
       <c r="C30" s="129" t="s">
         <v>62</v>
       </c>
@@ -4221,10 +4226,10 @@
       </c>
     </row>
     <row r="31" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="200" t="s">
+      <c r="A31" s="189" t="s">
         <v>87</v>
       </c>
-      <c r="B31" s="201"/>
+      <c r="B31" s="190"/>
       <c r="C31" s="134" t="s">
         <v>84</v>
       </c>
@@ -4274,10 +4279,10 @@
       </c>
     </row>
     <row r="32" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="200" t="s">
+      <c r="A32" s="189" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="201"/>
+      <c r="B32" s="190"/>
       <c r="C32" s="120" t="s">
         <v>68</v>
       </c>
@@ -4325,10 +4330,10 @@
       </c>
     </row>
     <row r="33" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="200" t="s">
+      <c r="A33" s="189" t="s">
         <v>89</v>
       </c>
-      <c r="B33" s="201"/>
+      <c r="B33" s="190"/>
       <c r="C33" s="135" t="s">
         <v>71</v>
       </c>
@@ -4376,10 +4381,10 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="200" t="s">
+      <c r="A34" s="189" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="201"/>
+      <c r="B34" s="190"/>
       <c r="C34" s="135" t="s">
         <v>74</v>
       </c>
@@ -4422,10 +4427,10 @@
       </c>
     </row>
     <row r="35" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="200" t="s">
+      <c r="A35" s="189" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="201"/>
+      <c r="B35" s="190"/>
       <c r="C35" s="135" t="s">
         <v>80</v>
       </c>
@@ -4473,11 +4478,11 @@
       </c>
     </row>
     <row r="36" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="202" t="s">
+      <c r="A36" s="191" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="202"/>
-      <c r="C36" s="203"/>
+      <c r="B36" s="191"/>
+      <c r="C36" s="192"/>
       <c r="D36" s="145"/>
       <c r="E36" s="136">
         <f t="shared" ref="E36:L36" si="8">SUM(E11:E35)</f>
@@ -4489,16 +4494,16 @@
       </c>
       <c r="G36" s="138">
         <f t="shared" si="8"/>
-        <v>4360591.8000000017</v>
+        <v>4559410.8000000026</v>
       </c>
       <c r="H36" s="138"/>
       <c r="I36" s="138">
         <f t="shared" si="8"/>
-        <v>224407.00000000009</v>
+        <v>25588.000000000095</v>
       </c>
       <c r="J36" s="139">
         <f t="shared" si="8"/>
-        <v>7027.746000000001</v>
+        <v>1063.1760000000015</v>
       </c>
       <c r="K36" s="139">
         <f t="shared" si="8"/>
@@ -4510,11 +4515,11 @@
       </c>
       <c r="M36" s="140">
         <f>SUM(M11:M28)</f>
-        <v>3790667.7100000004</v>
+        <v>3585883.7100000009</v>
       </c>
       <c r="N36" s="140">
         <f>SUM(N11:N35)</f>
-        <v>4152415.2500000009</v>
+        <v>3941487.2500000009</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4525,14 +4530,14 @@
       </c>
       <c r="G37" s="155">
         <f>SUMIF(H11:H35,"B",G11:G35)</f>
-        <v>3642735.4</v>
+        <v>3841554.4</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="204"/>
-      <c r="B38" s="204"/>
-      <c r="E38" s="205"/>
-      <c r="F38" s="206" t="s">
+      <c r="A38" s="182"/>
+      <c r="B38" s="182"/>
+      <c r="E38" s="183"/>
+      <c r="F38" s="184" t="s">
         <v>133</v>
       </c>
       <c r="G38" s="155">
@@ -4541,13 +4546,13 @@
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="204"/>
-      <c r="B39" s="204"/>
-      <c r="E39" s="205"/>
-      <c r="F39" s="206"/>
+      <c r="A39" s="182"/>
+      <c r="B39" s="182"/>
+      <c r="E39" s="183"/>
+      <c r="F39" s="184"/>
       <c r="G39" s="156">
         <f>SUM(G37:G38)</f>
-        <v>4161772.8</v>
+        <v>4360591.8</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -4574,6 +4579,19 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="E1:M1"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="A4:N8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="N9:N10"/>
     <mergeCell ref="A38:B39"/>
     <mergeCell ref="E38:E39"/>
     <mergeCell ref="F38:F39"/>
@@ -4589,19 +4607,6 @@
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A32:B32"/>
-    <mergeCell ref="E1:M1"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="A4:N8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="N9:N10"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
